--- a/cache/dienbao_ht.xlsx
+++ b/cache/dienbao_ht.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.15423347E12</v>
+        <v>8.29259754E12</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.75453533E12</v>
+        <v>1.74661777E12</v>
       </c>
     </row>
     <row r="8">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.7468342E11</v>
+        <v>3.337661E11</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.6195369E11</v>
+        <v>3.609056E11</v>
       </c>
     </row>
     <row r="10">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.00099549E12</v>
+        <v>1.03154611E12</v>
       </c>
     </row>
     <row r="11">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.98401768E12</v>
+        <v>3.02337655E12</v>
       </c>
     </row>
     <row r="12">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.319722913E13</v>
+        <v>1.343233884E13</v>
       </c>
     </row>
     <row r="13">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.060760544E13</v>
+        <v>1.079072563E13</v>
       </c>
     </row>
     <row r="14">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0715238E11</v>
+        <v>2.0375006E11</v>
       </c>
     </row>
     <row r="15">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.825E8</v>
+        <v>5.187E8</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.5795414E11</v>
+        <v>4.4713605E11</v>
       </c>
     </row>
     <row r="17">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.3176E8</v>
+        <v>7.3807E8</v>
       </c>
     </row>
     <row r="18">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.8130995E11</v>
+        <v>8.6599547E11</v>
       </c>
     </row>
     <row r="19">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.08321E9</v>
+        <v>1.13521E9</v>
       </c>
     </row>
     <row r="20">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.75007255E12</v>
+        <v>1.73404741E12</v>
       </c>
     </row>
     <row r="21">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.56273E9</v>
+        <v>1.49479E9</v>
       </c>
     </row>
     <row r="22">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.76766063E12</v>
+        <v>2.71141194E12</v>
       </c>
     </row>
     <row r="23">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.64066E9</v>
+        <v>2.64954E9</v>
       </c>
     </row>
     <row r="24">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.94004371E12</v>
+        <v>3.01150659E12</v>
       </c>
     </row>
     <row r="25">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.70811E9</v>
+        <v>3.89728E9</v>
       </c>
     </row>
     <row r="26">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.12E7</v>
+        <v>7.37E7</v>
       </c>
     </row>
     <row r="29">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.85E7</v>
+        <v>2.6E7</v>
       </c>
     </row>
     <row r="30">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.72537E11</v>
+        <v>7.1769402E11</v>
       </c>
     </row>
     <row r="33">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.8061E8</v>
+        <v>5.9344E8</v>
       </c>
     </row>
     <row r="34">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.19297E9</v>
+        <v>4.28297E9</v>
       </c>
     </row>
     <row r="35">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.108021E10</v>
+        <v>1.129385E10</v>
       </c>
     </row>
     <row r="39">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.39692E9</v>
+        <v>5.38997E9</v>
       </c>
     </row>
     <row r="40">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.58962369E12</v>
+        <v>2.64161321E12</v>
       </c>
     </row>
     <row r="41">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3.740096E10</v>
+        <v>3.671696E10</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.4315E8</v>
+        <v>1.2227E8</v>
       </c>
     </row>
     <row r="43">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.1438892E11</v>
+        <v>1.1457293E11</v>
       </c>
     </row>
     <row r="44">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.821E8</v>
+        <v>1.123E8</v>
       </c>
     </row>
     <row r="45">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9.042735E10</v>
+        <v>8.864685E10</v>
       </c>
     </row>
     <row r="46">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.7662E8</v>
+        <v>1.9962E8</v>
       </c>
     </row>
     <row r="47">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.61938653E12</v>
+        <v>1.58554203E12</v>
       </c>
     </row>
     <row r="48">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.01907E9</v>
+        <v>2.00149E9</v>
       </c>
     </row>
     <row r="49">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7.3865E10</v>
+        <v>7.5715E10</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.81177E9</v>
+        <v>2.51054E9</v>
       </c>
     </row>
     <row r="54">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.1363E9</v>
+        <v>1.3828E9</v>
       </c>
     </row>
     <row r="55">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.665837E10</v>
+        <v>2.334819E10</v>
       </c>
     </row>
     <row r="56">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5.983E9</v>
+        <v>7.95348E9</v>
       </c>
     </row>
     <row r="57">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.067537E10</v>
+        <v>1.539471E10</v>
       </c>
     </row>
     <row r="58">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8.613E9</v>
+        <v>1.0029E10</v>
       </c>
     </row>
     <row r="59">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.067217E10</v>
+        <v>1.066917E10</v>
       </c>
     </row>
     <row r="60">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3.2623803E11</v>
+        <v>3.5533583E11</v>
       </c>
     </row>
     <row r="65">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3.0032017E11</v>
+        <v>3.1878406E11</v>
       </c>
     </row>
     <row r="66">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5.308661E10</v>
+        <v>5.396575E10</v>
       </c>
     </row>
   </sheetData>
